--- a/BWI/bestwine_output/bestwine_Latvia.xlsx
+++ b/BWI/bestwine_output/bestwine_Latvia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA114"/>
+  <dimension ref="A1:AA116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -12764,6 +12764,200 @@
       <c r="Z114" s="2" t="inlineStr"/>
       <c r="AA114" s="2" t="inlineStr"/>
     </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Kabinett Sia</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Kabinett Sia</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>51763</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Rīga</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Rīga</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>18a Baznīcas iela</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>https://kabinett.lv</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>info@kabinett.lv</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr"/>
+      <c r="P115" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q115" s="2" t="inlineStr">
+        <is>
+          <t>41203041125</t>
+        </is>
+      </c>
+      <c r="R115" s="2" t="inlineStr"/>
+      <c r="S115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KabinettWineShop/</t>
+        </is>
+      </c>
+      <c r="T115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kabinettwineshop</t>
+        </is>
+      </c>
+      <c r="U115" s="2" t="inlineStr"/>
+      <c r="V115" s="2" t="inlineStr"/>
+      <c r="W115" s="2" t="inlineStr">
+        <is>
+          <t>Kristaps Eglitis</t>
+        </is>
+      </c>
+      <c r="X115" s="2" t="inlineStr">
+        <is>
+          <t>Founder/ Owner</t>
+        </is>
+      </c>
+      <c r="Y115" s="2" t="inlineStr"/>
+      <c r="Z115" s="2" t="inlineStr"/>
+      <c r="AA115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Kabinett Sia</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Kabinett Sia</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>51763</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Rīga</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Rīga</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>18a Baznīcas iela</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>https://kabinett.lv</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>info@kabinett.lv</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr"/>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
+          <t>41203041125</t>
+        </is>
+      </c>
+      <c r="R116" s="2" t="inlineStr"/>
+      <c r="S116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KabinettWineShop/</t>
+        </is>
+      </c>
+      <c r="T116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kabinettwineshop</t>
+        </is>
+      </c>
+      <c r="U116" s="2" t="inlineStr"/>
+      <c r="V116" s="2" t="inlineStr"/>
+      <c r="W116" s="2" t="inlineStr">
+        <is>
+          <t>Evija Sower</t>
+        </is>
+      </c>
+      <c r="X116" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y116" s="2" t="inlineStr"/>
+      <c r="Z116" s="2" t="inlineStr"/>
+      <c r="AA116" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Latvia.xlsx
+++ b/BWI/bestwine_output/bestwine_Latvia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA116"/>
+  <dimension ref="A1:AA118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -12958,6 +12958,200 @@
       <c r="Z116" s="2" t="inlineStr"/>
       <c r="AA116" s="2" t="inlineStr"/>
     </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Kabinett Sia</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Kabinett Sia</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>51763</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Rīga</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Rīga</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>18a Baznīcas iela</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>https://kabinett.lv</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr"/>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr"/>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>info@kabinett.lv</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr"/>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q117" s="2" t="inlineStr">
+        <is>
+          <t>41203041125</t>
+        </is>
+      </c>
+      <c r="R117" s="2" t="inlineStr"/>
+      <c r="S117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KabinettWineShop/</t>
+        </is>
+      </c>
+      <c r="T117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kabinettwineshop</t>
+        </is>
+      </c>
+      <c r="U117" s="2" t="inlineStr"/>
+      <c r="V117" s="2" t="inlineStr"/>
+      <c r="W117" s="2" t="inlineStr">
+        <is>
+          <t>Kristaps Eglitis</t>
+        </is>
+      </c>
+      <c r="X117" s="2" t="inlineStr">
+        <is>
+          <t>Founder/ Owner</t>
+        </is>
+      </c>
+      <c r="Y117" s="2" t="inlineStr"/>
+      <c r="Z117" s="2" t="inlineStr"/>
+      <c r="AA117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Kabinett Sia</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Kabinett Sia</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>51763</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Rīga</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Rīga</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>18a Baznīcas iela</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>https://kabinett.lv</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>info@kabinett.lv</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr"/>
+      <c r="P118" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q118" s="2" t="inlineStr">
+        <is>
+          <t>41203041125</t>
+        </is>
+      </c>
+      <c r="R118" s="2" t="inlineStr"/>
+      <c r="S118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KabinettWineShop/</t>
+        </is>
+      </c>
+      <c r="T118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kabinettwineshop</t>
+        </is>
+      </c>
+      <c r="U118" s="2" t="inlineStr"/>
+      <c r="V118" s="2" t="inlineStr"/>
+      <c r="W118" s="2" t="inlineStr">
+        <is>
+          <t>Evija Sower</t>
+        </is>
+      </c>
+      <c r="X118" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y118" s="2" t="inlineStr"/>
+      <c r="Z118" s="2" t="inlineStr"/>
+      <c r="AA118" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Latvia.xlsx
+++ b/BWI/bestwine_output/bestwine_Latvia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA118"/>
+  <dimension ref="A1:AA121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -13152,6 +13152,297 @@
       <c r="Z118" s="2" t="inlineStr"/>
       <c r="AA118" s="2" t="inlineStr"/>
     </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Verdens Sia</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Verdens Sia</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>27449</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Rīga</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Rīga</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>12 Bērzaunes iela</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>https://verdens.lv</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr"/>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr"/>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>chateau@verdens.lv</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr"/>
+      <c r="P119" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q119" s="2" t="inlineStr">
+        <is>
+          <t>50103269091</t>
+        </is>
+      </c>
+      <c r="R119" s="2" t="inlineStr"/>
+      <c r="S119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/chateauverdens/</t>
+        </is>
+      </c>
+      <c r="T119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chateau.verdens</t>
+        </is>
+      </c>
+      <c r="U119" s="2" t="inlineStr"/>
+      <c r="V119" s="2" t="inlineStr"/>
+      <c r="W119" s="2" t="inlineStr">
+        <is>
+          <t>Ruslans Verdens</t>
+        </is>
+      </c>
+      <c r="X119" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y119" s="2" t="inlineStr"/>
+      <c r="Z119" s="2" t="inlineStr"/>
+      <c r="AA119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Kabinett Sia</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Kabinett Sia</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>51763</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Rīga</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Rīga</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>18a Baznīcas iela</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>https://kabinett.lv</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>info@kabinett.lv</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr"/>
+      <c r="P120" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q120" s="2" t="inlineStr">
+        <is>
+          <t>41203041125</t>
+        </is>
+      </c>
+      <c r="R120" s="2" t="inlineStr"/>
+      <c r="S120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KabinettWineShop/</t>
+        </is>
+      </c>
+      <c r="T120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kabinettwineshop</t>
+        </is>
+      </c>
+      <c r="U120" s="2" t="inlineStr"/>
+      <c r="V120" s="2" t="inlineStr"/>
+      <c r="W120" s="2" t="inlineStr">
+        <is>
+          <t>Kristaps Eglitis</t>
+        </is>
+      </c>
+      <c r="X120" s="2" t="inlineStr">
+        <is>
+          <t>Founder/ Owner</t>
+        </is>
+      </c>
+      <c r="Y120" s="2" t="inlineStr"/>
+      <c r="Z120" s="2" t="inlineStr"/>
+      <c r="AA120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Kabinett Sia</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Kabinett Sia</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>51763</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Rīga</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Rīga</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>18a Baznīcas iela</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>https://kabinett.lv</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr"/>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr"/>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>info@kabinett.lv</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr"/>
+      <c r="P121" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q121" s="2" t="inlineStr">
+        <is>
+          <t>41203041125</t>
+        </is>
+      </c>
+      <c r="R121" s="2" t="inlineStr"/>
+      <c r="S121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KabinettWineShop/</t>
+        </is>
+      </c>
+      <c r="T121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kabinettwineshop</t>
+        </is>
+      </c>
+      <c r="U121" s="2" t="inlineStr"/>
+      <c r="V121" s="2" t="inlineStr"/>
+      <c r="W121" s="2" t="inlineStr">
+        <is>
+          <t>Evija Sower</t>
+        </is>
+      </c>
+      <c r="X121" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y121" s="2" t="inlineStr"/>
+      <c r="Z121" s="2" t="inlineStr"/>
+      <c r="AA121" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Latvia.xlsx
+++ b/BWI/bestwine_output/bestwine_Latvia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA121"/>
+  <dimension ref="A1:AA126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -13443,6 +13443,499 @@
       <c r="Z121" s="2" t="inlineStr"/>
       <c r="AA121" s="2" t="inlineStr"/>
     </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Stream Distribution Sia</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Stream Distribution Sia</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>108928</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Mārupe</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Mārupes novads</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>5 Plieņciema Iela</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>2167</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.drinksdrinks.lv</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>office@streamdistribution.lv</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr"/>
+      <c r="P122" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q122" s="2" t="inlineStr">
+        <is>
+          <t>40203119588</t>
+        </is>
+      </c>
+      <c r="R122" s="2" t="inlineStr"/>
+      <c r="S122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/drinksanddrinks/</t>
+        </is>
+      </c>
+      <c r="T122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/drinks_n_drinks</t>
+        </is>
+      </c>
+      <c r="U122" s="2" t="inlineStr"/>
+      <c r="V122" s="2" t="inlineStr"/>
+      <c r="W122" s="2" t="inlineStr">
+        <is>
+          <t>Valts Ermansons</t>
+        </is>
+      </c>
+      <c r="X122" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director/ Co-owner</t>
+        </is>
+      </c>
+      <c r="Y122" s="2" t="inlineStr"/>
+      <c r="Z122" s="2" t="inlineStr"/>
+      <c r="AA122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/valts-ermansons-94a5a72/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Stream Distribution Sia</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Stream Distribution Sia</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>108928</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Mārupe</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Mārupes novads</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>5 Plieņciema Iela</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>2167</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.drinksdrinks.lv</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr"/>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr"/>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>office@streamdistribution.lv</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr"/>
+      <c r="P123" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
+          <t>40203119588</t>
+        </is>
+      </c>
+      <c r="R123" s="2" t="inlineStr"/>
+      <c r="S123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/drinksanddrinks/</t>
+        </is>
+      </c>
+      <c r="T123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/drinks_n_drinks</t>
+        </is>
+      </c>
+      <c r="U123" s="2" t="inlineStr"/>
+      <c r="V123" s="2" t="inlineStr"/>
+      <c r="W123" s="2" t="inlineStr">
+        <is>
+          <t>Krista Kokina</t>
+        </is>
+      </c>
+      <c r="X123" s="2" t="inlineStr">
+        <is>
+          <t>Store Manager</t>
+        </is>
+      </c>
+      <c r="Y123" s="2" t="inlineStr"/>
+      <c r="Z123" s="2" t="inlineStr"/>
+      <c r="AA123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/krista-kokina-10095065/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Verdens Sia</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Verdens Sia</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>27449</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Rīga</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Rīga</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>12 Bērzaunes iela</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>https://verdens.lv</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>chateau@verdens.lv</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr"/>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>50103269091</t>
+        </is>
+      </c>
+      <c r="R124" s="2" t="inlineStr"/>
+      <c r="S124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/chateauverdens/</t>
+        </is>
+      </c>
+      <c r="T124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chateau.verdens</t>
+        </is>
+      </c>
+      <c r="U124" s="2" t="inlineStr"/>
+      <c r="V124" s="2" t="inlineStr"/>
+      <c r="W124" s="2" t="inlineStr">
+        <is>
+          <t>Ruslans Verdens</t>
+        </is>
+      </c>
+      <c r="X124" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y124" s="2" t="inlineStr"/>
+      <c r="Z124" s="2" t="inlineStr"/>
+      <c r="AA124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Kabinett Sia</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Kabinett Sia</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>51763</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Rīga</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Rīga</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>18a Baznīcas iela</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>https://kabinett.lv</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr"/>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>info@kabinett.lv</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr"/>
+      <c r="P125" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t>41203041125</t>
+        </is>
+      </c>
+      <c r="R125" s="2" t="inlineStr"/>
+      <c r="S125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KabinettWineShop/</t>
+        </is>
+      </c>
+      <c r="T125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kabinettwineshop</t>
+        </is>
+      </c>
+      <c r="U125" s="2" t="inlineStr"/>
+      <c r="V125" s="2" t="inlineStr"/>
+      <c r="W125" s="2" t="inlineStr">
+        <is>
+          <t>Kristaps Eglitis</t>
+        </is>
+      </c>
+      <c r="X125" s="2" t="inlineStr">
+        <is>
+          <t>Founder/ Owner</t>
+        </is>
+      </c>
+      <c r="Y125" s="2" t="inlineStr"/>
+      <c r="Z125" s="2" t="inlineStr"/>
+      <c r="AA125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Kabinett Sia</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Kabinett Sia</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>51763</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Rīga</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Rīga</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>18a Baznīcas iela</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>https://kabinett.lv</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr"/>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>info@kabinett.lv</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr"/>
+      <c r="P126" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>41203041125</t>
+        </is>
+      </c>
+      <c r="R126" s="2" t="inlineStr"/>
+      <c r="S126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KabinettWineShop/</t>
+        </is>
+      </c>
+      <c r="T126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kabinettwineshop</t>
+        </is>
+      </c>
+      <c r="U126" s="2" t="inlineStr"/>
+      <c r="V126" s="2" t="inlineStr"/>
+      <c r="W126" s="2" t="inlineStr">
+        <is>
+          <t>Evija Sower</t>
+        </is>
+      </c>
+      <c r="X126" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y126" s="2" t="inlineStr"/>
+      <c r="Z126" s="2" t="inlineStr"/>
+      <c r="AA126" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
